--- a/Simulation Results/CEC2017/CEC2017.xlsx
+++ b/Simulation Results/CEC2017/CEC2017.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FIM\Matlab\FIM (Comparison)  Add SWO\Results and Graphs\Final results\CEC2017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RESEARCH\Matlab\FIM\Matlab\FIM (Comparison)  Paper Version\Results and Graphs\Final results\CEC2017 10D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84DC218-D7B4-4AE1-813D-482701945AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616E1775-6717-47BB-956E-D2D87FE09401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="13" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="13" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="F13" sheetId="39" r:id="rId12"/>
     <sheet name="F14" sheetId="30" r:id="rId13"/>
     <sheet name="F15" sheetId="31" r:id="rId14"/>
-    <sheet name="F16" sheetId="40" r:id="rId15"/>
+    <sheet name="F16" sheetId="49" r:id="rId15"/>
     <sheet name="F17" sheetId="41" r:id="rId16"/>
     <sheet name="F18" sheetId="32" r:id="rId17"/>
     <sheet name="F19" sheetId="18" r:id="rId18"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="50">
   <si>
     <t>Algorithm</t>
   </si>
@@ -212,9 +212,6 @@
   <si>
     <t>Rank</t>
   </si>
-  <si>
-    <t>F16</t>
-  </si>
 </sst>
 </file>
 
@@ -283,6 +280,111 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ConvergencePlot">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AD1A07B-68DC-48DF-AFEB-3606E84C319C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1270000" y="1270000"/>
+          <a:ext cx="5080000" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="BoxPlot">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2551F73B-B9E8-4871-A202-89EB82F1D9BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1270000" y="5334000"/>
+          <a:ext cx="5080000" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -655,16 +757,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AY17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="11" width="15.53125" customWidth="1"/>
-    <col min="12" max="12" width="11.53125" customWidth="1"/>
-    <col min="13" max="31" width="15.53125" customWidth="1"/>
-    <col min="32" max="32" width="11.53125" customWidth="1"/>
-    <col min="33" max="34" width="15.53125" customWidth="1"/>
-    <col min="35" max="35" width="11.53125" customWidth="1"/>
-    <col min="36" max="36" width="15.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="11" width="15.54296875" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" customWidth="1"/>
+    <col min="13" max="31" width="15.54296875" customWidth="1"/>
+    <col min="32" max="32" width="11.54296875" customWidth="1"/>
+    <col min="33" max="34" width="15.54296875" customWidth="1"/>
+    <col min="35" max="35" width="11.54296875" customWidth="1"/>
+    <col min="36" max="36" width="15.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2273,10 +2375,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3870,12 +3972,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="34" width="11.53125" customWidth="1"/>
-    <col min="35" max="35" width="15.19921875" customWidth="1"/>
-    <col min="36" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="34" width="11.54296875" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5469,12 +5571,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05358831-F504-4B75-94E8-546525BDBCF8}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -7067,10 +7169,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CA9175-CF52-48F8-BEBE-BA1653452C1C}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8664,12 +8766,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37A6879-2E55-444D-BFBC-6B30F99754B7}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -10260,1614 +10362,1614 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB323DB7-9709-47ED-8B14-27B8A06AC994}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B59F3730-3745-4894-8983-30E6D974758E}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="34" width="11.53125" style="3" customWidth="1"/>
-    <col min="35" max="35" width="12.53125" style="3" customWidth="1"/>
-    <col min="36" max="36" width="11.53125" style="3" customWidth="1"/>
-    <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="1" max="1" width="9.08984375" customWidth="1"/>
+    <col min="2" max="34" width="11.453125" customWidth="1"/>
+    <col min="35" max="35" width="12.453125" customWidth="1"/>
+    <col min="36" max="36" width="11.453125" customWidth="1"/>
+    <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
-      <c r="A1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>29</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" t="s">
         <v>30</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" t="s">
         <v>36</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>37</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" t="s">
         <v>41</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" t="s">
         <v>42</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" t="s">
         <v>43</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" t="s">
         <v>44</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" t="s">
         <v>45</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" t="s">
         <v>46</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" t="s">
         <v>47</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" t="s">
         <v>48</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>1601.3073133185635</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1600.7392022845575</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1601.2725341057489</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1601.0131010101431</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1601.288018235829</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1600.9844809176359</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1601.1651949528534</v>
-      </c>
-      <c r="I2" s="4">
-        <v>1600.8541728120724</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1601.1995387907268</v>
-      </c>
-      <c r="K2" s="4">
-        <v>1600.6283489955149</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1601.0052032826086</v>
-      </c>
-      <c r="M2" s="4">
-        <v>1601.3646804301243</v>
-      </c>
-      <c r="N2" s="4">
-        <v>1600.5065851098502</v>
-      </c>
-      <c r="O2" s="4">
-        <v>1601.012179350219</v>
-      </c>
-      <c r="P2" s="4">
-        <v>1600.3197771623518</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>1601.2722312507424</v>
-      </c>
-      <c r="R2" s="4">
-        <v>1601.1699238842878</v>
-      </c>
-      <c r="S2" s="4">
-        <v>1601.1574908999535</v>
-      </c>
-      <c r="T2" s="4">
-        <v>1601.2204576924289</v>
-      </c>
-      <c r="U2" s="4">
-        <v>1600.9767435196495</v>
-      </c>
-      <c r="V2" s="4">
-        <v>1601.2645256350525</v>
-      </c>
-      <c r="W2" s="4">
-        <v>1601.0998280366257</v>
-      </c>
-      <c r="X2" s="4">
-        <v>1601.3543339421165</v>
-      </c>
-      <c r="Y2" s="4">
-        <v>1600.0243021626757</v>
-      </c>
-      <c r="Z2" s="4">
-        <v>1600.2581931149662</v>
-      </c>
-      <c r="AA2" s="4">
-        <v>1600.715655321294</v>
-      </c>
-      <c r="AB2" s="4">
-        <v>1601.236023677907</v>
-      </c>
-      <c r="AC2" s="4">
-        <v>1601.0864142583932</v>
-      </c>
-      <c r="AD2" s="4">
-        <v>1600.040021384897</v>
-      </c>
-      <c r="AE2" s="4">
-        <v>1601.0438099244357</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>1600.0243021626757</v>
-      </c>
-      <c r="AG2" s="4">
-        <v>1600.952676182141</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>1601.3646804301243</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>0.38376206922373429</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>1601.0651120914144</v>
-      </c>
-      <c r="AK2" s="4">
+      <c r="B2" s="2">
+        <v>1601.4776138689635</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1601.236646205145</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1600.6950246061958</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1600.7104775957589</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1600.5264968258766</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1600.9542526131172</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1601.3984098367971</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1601.0277559718709</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1601.4031432492902</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1601.4067364188895</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1601.1268632226115</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1600.967728031068</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1601.4485348392482</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1600.2718533122647</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1601.3765234054695</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1601.324476182549</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1601.3611515711859</v>
+      </c>
+      <c r="S2" s="2">
+        <v>1601.1953359902054</v>
+      </c>
+      <c r="T2" s="2">
+        <v>1601.4970665730975</v>
+      </c>
+      <c r="U2" s="2">
+        <v>1600.971302506246</v>
+      </c>
+      <c r="V2" s="2">
+        <v>1601.4211685309012</v>
+      </c>
+      <c r="W2" s="2">
+        <v>1601.382690631387</v>
+      </c>
+      <c r="X2" s="2">
+        <v>1601.2928545836126</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>1601.4922078565776</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>1601.3955553310664</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>1601.4370616950632</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>1600.9148207902938</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>1601.4383854830542</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>1601.2666482416828</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>1601.0308074943725</v>
+      </c>
+      <c r="AF2">
+        <v>1600.2718533122647</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>1601.1816531154618</v>
+      </c>
+      <c r="AH2">
+        <v>1601.4970665730975</v>
+      </c>
+      <c r="AI2">
+        <v>0.31446017411807237</v>
+      </c>
+      <c r="AJ2">
+        <v>1601.3086653830808</v>
+      </c>
+      <c r="AK2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>2654.7133281650345</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2881.7450992912832</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2748.8550103025668</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2659.4089985166438</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2670.3577725850737</v>
-      </c>
-      <c r="G3" s="3">
-        <v>2593.7771164534179</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2945.1631404549394</v>
-      </c>
-      <c r="I3" s="3">
-        <v>2982.4133960595568</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2635.9443762062328</v>
-      </c>
-      <c r="K3" s="3">
-        <v>2550.1413123917177</v>
-      </c>
-      <c r="L3" s="3">
-        <v>2875.4151522631591</v>
-      </c>
-      <c r="M3" s="3">
-        <v>2838.1503713302045</v>
-      </c>
-      <c r="N3" s="3">
-        <v>3281.1173700044956</v>
-      </c>
-      <c r="O3" s="3">
-        <v>2758.5653850624385</v>
-      </c>
-      <c r="P3" s="3">
-        <v>2572.1782417598833</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>2253.6052800088855</v>
-      </c>
-      <c r="R3" s="3">
-        <v>2878.5779936727668</v>
-      </c>
-      <c r="S3" s="3">
-        <v>2290.9718597538595</v>
-      </c>
-      <c r="T3" s="3">
-        <v>3317.5514992942826</v>
-      </c>
-      <c r="U3" s="3">
-        <v>3416.7449626371736</v>
-      </c>
-      <c r="V3" s="3">
-        <v>2495.0558813034263</v>
-      </c>
-      <c r="W3" s="3">
-        <v>3288.0851589646927</v>
-      </c>
-      <c r="X3" s="3">
-        <v>2574.2827241030373</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>3222.5278372596158</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>2487.0423985129073</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>2195.5812228597019</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>2691.2212800678963</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>2543.5995814333223</v>
-      </c>
-      <c r="AD3" s="3">
-        <v>2878.3004017970748</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>2853.475250690115</v>
-      </c>
-      <c r="AF3" s="3">
-        <v>2195.5812228597019</v>
-      </c>
-      <c r="AG3" s="3">
-        <v>2767.8189801068479</v>
-      </c>
-      <c r="AH3" s="3">
-        <v>3416.7449626371736</v>
-      </c>
-      <c r="AI3" s="3">
-        <v>312.7715900243283</v>
-      </c>
-      <c r="AJ3" s="3">
-        <v>2720.0381451852318</v>
-      </c>
-      <c r="AK3" s="3">
+      <c r="B3" s="1">
+        <v>2549.5852543194574</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2793.6215738444848</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2897.4885975240886</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2790.5167221861216</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2583.6247433388771</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3184.6016560201192</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2830.4876784650028</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2498.9631961203199</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2530.1922501957943</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2710.5070872655747</v>
+      </c>
+      <c r="L3" s="1">
+        <v>2970.4659992476563</v>
+      </c>
+      <c r="M3" s="1">
+        <v>2870.7149677884222</v>
+      </c>
+      <c r="N3" s="1">
+        <v>2807.1301768688918</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2687.395104274407</v>
+      </c>
+      <c r="P3" s="1">
+        <v>2872.6440142134179</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>2800.1431906274161</v>
+      </c>
+      <c r="R3" s="1">
+        <v>2562.5056231633812</v>
+      </c>
+      <c r="S3" s="1">
+        <v>2864.5059112492895</v>
+      </c>
+      <c r="T3" s="1">
+        <v>2889.510332583694</v>
+      </c>
+      <c r="U3" s="1">
+        <v>2790.8634429795225</v>
+      </c>
+      <c r="V3" s="1">
+        <v>2486.3671631740226</v>
+      </c>
+      <c r="W3" s="1">
+        <v>2864.0164323512472</v>
+      </c>
+      <c r="X3" s="1">
+        <v>2853.0091858478954</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>2473.6670997548272</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>2776.9717065638351</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>2758.3203699092696</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>2748.2550858797213</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>2525.4720124810601</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>2658.4068014624172</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>2364.3562248750768</v>
+      </c>
+      <c r="AF3">
+        <v>2364.3562248750768</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>2733.143653485844</v>
+      </c>
+      <c r="AH3">
+        <v>3184.6016560201192</v>
+      </c>
+      <c r="AI3">
+        <v>178.88374974976892</v>
+      </c>
+      <c r="AJ3">
+        <v>2783.7442143749786</v>
+      </c>
+      <c r="AK3" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>2097.3253991785641</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2222.3526136474584</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2395.6991418093262</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1817.8935703194904</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2260.0726923884868</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2120.5549887121165</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2420.5353223130251</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2285.5813205508916</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2189.1065757589849</v>
-      </c>
-      <c r="K4" s="3">
-        <v>2187.9899377447155</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1943.5345463571821</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1837.1317624461699</v>
-      </c>
-      <c r="N4" s="3">
-        <v>2003.4322506590684</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1890.2517292781158</v>
-      </c>
-      <c r="P4" s="3">
-        <v>2328.0280687852614</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>2205.5468100855073</v>
-      </c>
-      <c r="R4" s="3">
-        <v>2165.9288564691269</v>
-      </c>
-      <c r="S4" s="3">
-        <v>2260.8672230541051</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1995.2340607585727</v>
-      </c>
-      <c r="U4" s="3">
-        <v>2052.0051043188951</v>
-      </c>
-      <c r="V4" s="3">
-        <v>2304.3006140834004</v>
-      </c>
-      <c r="W4" s="3">
-        <v>2366.5789286411509</v>
-      </c>
-      <c r="X4" s="3">
-        <v>2034.5555622186723</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>2183.2179366567079</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>2189.1305397370911</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>2454.6933620970813</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>2224.2591548288833</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>2179.1018029492761</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>2031.8079514146302</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>2058.1851559166998</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>1817.8935703194904</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>2156.8300994392889</v>
-      </c>
-      <c r="AH4" s="3">
-        <v>2454.6933620970813</v>
-      </c>
-      <c r="AI4" s="3">
-        <v>166.44579093598651</v>
-      </c>
-      <c r="AJ4" s="3">
-        <v>2185.6039372007117</v>
-      </c>
-      <c r="AK4" s="3">
-        <v>11</v>
+      <c r="B4" s="1">
+        <v>2325.8458667990872</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1937.7877066521103</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2051.0623322657339</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2540.2683543631292</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2431.7251978122072</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1923.9971938180192</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1998.2903075883457</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2189.4742841901261</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2120.2514742847725</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2169.1989330635556</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2268.3603807526115</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1988.3023123578096</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2065.9380601920066</v>
+      </c>
+      <c r="O4" s="1">
+        <v>2241.221191215287</v>
+      </c>
+      <c r="P4" s="1">
+        <v>2181.9419749190292</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>2020.0208971817299</v>
+      </c>
+      <c r="R4" s="1">
+        <v>1716.835054811994</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1980.3249002290324</v>
+      </c>
+      <c r="T4" s="1">
+        <v>2399.9581165476566</v>
+      </c>
+      <c r="U4" s="1">
+        <v>2291.4393899891957</v>
+      </c>
+      <c r="V4" s="1">
+        <v>2216.1804274101037</v>
+      </c>
+      <c r="W4" s="1">
+        <v>2292.1190069298345</v>
+      </c>
+      <c r="X4" s="1">
+        <v>1834.9587844563891</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>2181.3640663782162</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>2201.144418040064</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>2096.310076459597</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>2046.6697333214788</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>2052.6751160281542</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>1912.1248356425667</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>1950.7847724350534</v>
+      </c>
+      <c r="AF4">
+        <v>1716.835054811994</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>2120.8858388711624</v>
+      </c>
+      <c r="AH4">
+        <v>2540.2683543631292</v>
+      </c>
+      <c r="AI4">
+        <v>184.57721117455199</v>
+      </c>
+      <c r="AJ4">
+        <v>2108.2807753721845</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:37">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1699.267055659988</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1665.831723189958</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2024.801141892438</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1804.2902924562609</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1771.4003567351563</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1945.9764607058983</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1878.5417639121947</v>
-      </c>
-      <c r="I5" s="3">
-        <v>2049.5079201874514</v>
-      </c>
-      <c r="J5" s="3">
-        <v>1806.4892906623543</v>
-      </c>
-      <c r="K5" s="3">
-        <v>2058.7689076315514</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1773.3446981827537</v>
-      </c>
-      <c r="M5" s="3">
-        <v>1749.3439344406991</v>
-      </c>
-      <c r="N5" s="3">
-        <v>1894.9247618192519</v>
-      </c>
-      <c r="O5" s="3">
-        <v>1740.1278117324816</v>
-      </c>
-      <c r="P5" s="3">
-        <v>2111.8482275266047</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>2142.2111037903514</v>
-      </c>
-      <c r="R5" s="3">
-        <v>1825.7208578947052</v>
-      </c>
-      <c r="S5" s="3">
-        <v>1986.9391856226416</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1819.763550378746</v>
-      </c>
-      <c r="U5" s="3">
-        <v>1740.2076485778623</v>
-      </c>
-      <c r="V5" s="3">
-        <v>1845.3394165128589</v>
-      </c>
-      <c r="W5" s="3">
-        <v>1752.0792724472185</v>
-      </c>
-      <c r="X5" s="3">
-        <v>1991.9704683560128</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>1727.5472634172459</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>2025.9923577156706</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>2103.2567083616987</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>1844.1284372161056</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>1694.8712731913936</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>2092.6615421776578</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>1807.3959990881212</v>
-      </c>
-      <c r="AF5" s="3">
-        <v>1665.831723189958</v>
-      </c>
-      <c r="AG5" s="3">
-        <v>1879.1516477161106</v>
-      </c>
-      <c r="AH5" s="3">
-        <v>2142.2111037903514</v>
-      </c>
-      <c r="AI5" s="3">
-        <v>144.59284383164993</v>
-      </c>
-      <c r="AJ5" s="3">
-        <v>1834.9246475554055</v>
-      </c>
-      <c r="AK5" s="3">
+      <c r="B5" s="1">
+        <v>1785.2470651144001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1806.512536777718</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1826.1890826651238</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1927.0829143860483</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1805.306399131777</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1733.0161477683725</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1824.4299979369414</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1780.8500474200944</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1832.3364485279603</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1870.7886584839132</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2084.8260833954541</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1968.747736572172</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1630.0768302626605</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1754.1768033903343</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1651.0377491737017</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1725.5122526992029</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1764.8411153096126</v>
+      </c>
+      <c r="S5" s="1">
+        <v>2000.016783048758</v>
+      </c>
+      <c r="T5" s="1">
+        <v>2003.9808114086766</v>
+      </c>
+      <c r="U5" s="1">
+        <v>1634.0592795044522</v>
+      </c>
+      <c r="V5" s="1">
+        <v>2005.6924892984302</v>
+      </c>
+      <c r="W5" s="1">
+        <v>2086.7951298916114</v>
+      </c>
+      <c r="X5" s="1">
+        <v>2074.7326741858424</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1713.3428018444113</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1842.6818931090838</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>1878.2121987027867</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>1819.4050822723982</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>2096.9996443273831</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>1792.4570798422371</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>1669.5272158009022</v>
+      </c>
+      <c r="AF5">
+        <v>1630.0768302626605</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>1846.2960317417483</v>
+      </c>
+      <c r="AH5">
+        <v>2096.9996443273831</v>
+      </c>
+      <c r="AI5">
+        <v>139.47995251348868</v>
+      </c>
+      <c r="AJ5">
+        <v>1821.9175401046698</v>
+      </c>
+      <c r="AK5" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1690.9957367451543</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1663.9763977143584</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1655.65232985437</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1763.7931246665125</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1640.036210245373</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1705.9878785033611</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1758.3871412525023</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1655.555093631388</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1799.2364927329381</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1685.8860656535155</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1652.776883029904</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1674.75030968697</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1741.6114842152444</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1668.8941972973496</v>
-      </c>
-      <c r="P6" s="3">
-        <v>1695.1347398877883</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>1725.7459067003083</v>
-      </c>
-      <c r="R6" s="3">
-        <v>1733.9576926773134</v>
-      </c>
-      <c r="S6" s="3">
-        <v>1655.758577567794</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1696.2096833680534</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1703.6311567093135</v>
-      </c>
-      <c r="V6" s="3">
-        <v>1705.1850261478753</v>
-      </c>
-      <c r="W6" s="3">
-        <v>1718.1424315628706</v>
-      </c>
-      <c r="X6" s="3">
-        <v>1662.2603187925104</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1676.7849150934937</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>1713.4305917600248</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>1701.7409439503933</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>1752.4764113398589</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>1711.7514607119319</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>1751.4798629604666</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>1713.467453836699</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>1640.036210245373</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>1702.4898839431874</v>
-      </c>
-      <c r="AH6" s="3">
-        <v>1799.2364927329381</v>
-      </c>
-      <c r="AI6" s="3">
-        <v>38.911623433041584</v>
-      </c>
-      <c r="AJ6" s="3">
-        <v>1702.6860503298535</v>
-      </c>
-      <c r="AK6" s="3">
-        <v>2</v>
+      <c r="B6" s="1">
+        <v>1632.8484917055791</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1687.1744970484915</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1711.2176951305382</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1739.318634611315</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1783.7174126319976</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1688.3773905088858</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1668.899056706606</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1753.1128313879458</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1718.4049588975865</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1629.5425428472265</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1708.600288341491</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1778.859593709954</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1662.6772026747537</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1756.6037831559368</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1674.4608772391928</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1675.284368141093</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1760.6405433638174</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1662.2188080809424</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1790.9203185780902</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1637.1926152285421</v>
+      </c>
+      <c r="V6" s="1">
+        <v>1683.174671253639</v>
+      </c>
+      <c r="W6" s="1">
+        <v>1693.0127133764604</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1637.1752046404151</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1717.4364407947596</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1681.8223872239173</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>1768.2959122215536</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>1689.1289452768483</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>1649.0134045670329</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1677.0216544353966</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>1774.4515241025879</v>
+      </c>
+      <c r="AF6">
+        <v>1629.5425428472265</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>1703.0201589294199</v>
+      </c>
+      <c r="AH6">
+        <v>1790.9203185780902</v>
+      </c>
+      <c r="AI6">
+        <v>49.180264524564684</v>
+      </c>
+      <c r="AJ6">
+        <v>1688.7531678928672</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
-        <v>2385.3273323558055</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2079.3364782593035</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2504.0039980735237</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2430.6062514349242</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2430.7024593874639</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2752.5821243791252</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2418.6741277238611</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2256.0002368271521</v>
-      </c>
-      <c r="J7" s="3">
-        <v>2808.7501235606524</v>
-      </c>
-      <c r="K7" s="3">
-        <v>2504.4269294351438</v>
-      </c>
-      <c r="L7" s="3">
-        <v>2486.3084373840124</v>
-      </c>
-      <c r="M7" s="3">
-        <v>2635.9303942186289</v>
-      </c>
-      <c r="N7" s="3">
-        <v>2749.4371248938251</v>
-      </c>
-      <c r="O7" s="3">
-        <v>2955.0838426876903</v>
-      </c>
-      <c r="P7" s="3">
-        <v>2313.25569051395</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>2712.6564445372328</v>
-      </c>
-      <c r="R7" s="3">
-        <v>2619.7720894716704</v>
-      </c>
-      <c r="S7" s="3">
-        <v>2528.1747611163019</v>
-      </c>
-      <c r="T7" s="3">
-        <v>2354.822036269718</v>
-      </c>
-      <c r="U7" s="3">
-        <v>2757.3572285730952</v>
-      </c>
-      <c r="V7" s="3">
-        <v>2575.4153616200874</v>
-      </c>
-      <c r="W7" s="3">
-        <v>2271.8358171286773</v>
-      </c>
-      <c r="X7" s="3">
-        <v>2884.8349257587283</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>2201.8637191553066</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>2323.190299303149</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>1995.2393911737477</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>2314.3518388593629</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>2353.022104505339</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>2489.367960417208</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>2405.2002424717894</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>1995.2393911737477</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>2483.2509923832158</v>
-      </c>
-      <c r="AH7" s="3">
-        <v>2955.0838426876903</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>229.9243416720758</v>
-      </c>
-      <c r="AJ7" s="3">
-        <v>2458.5054483857384</v>
-      </c>
-      <c r="AK7" s="3">
+      <c r="B7" s="1">
+        <v>2175.2187060450042</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2699.2807116166973</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2229.7059028248805</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2857.8436792599173</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2286.2803417158257</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2354.0769260963416</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2483.8483517830059</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2173.517441982081</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2717.8087298048326</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2600.1202703179815</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2496.5853165218869</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2422.3273417889995</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2516.7743920214361</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2360.7683535625983</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2918.501586502909</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2246.9894986144518</v>
+      </c>
+      <c r="R7" s="1">
+        <v>2250.9084505844667</v>
+      </c>
+      <c r="S7" s="1">
+        <v>2837.8034648937873</v>
+      </c>
+      <c r="T7" s="1">
+        <v>2810.3897961189623</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2416.5503264705244</v>
+      </c>
+      <c r="V7" s="1">
+        <v>2306.6877820262844</v>
+      </c>
+      <c r="W7" s="1">
+        <v>2518.7556064376313</v>
+      </c>
+      <c r="X7" s="1">
+        <v>2355.8359316166898</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>2242.2595877595018</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>2602.6371938774819</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>2313.1033654153835</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>2607.9266338089146</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>2338.617293204326</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>2353.1118718577136</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2618.1420306188438</v>
+      </c>
+      <c r="AF7">
+        <v>2173.517441982081</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>2470.4125628383117</v>
+      </c>
+      <c r="AH7">
+        <v>2918.501586502909</v>
+      </c>
+      <c r="AI7">
+        <v>214.90085022359776</v>
+      </c>
+      <c r="AJ7">
+        <v>2419.4388341297617</v>
+      </c>
+      <c r="AK7" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:37">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>1743.1831400181613</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1622.156304256863</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1766.1085453649475</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1851.8347991012236</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1619.6205578064532</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1610.6463448892705</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1767.1283475634657</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1747.2434228055026</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1639.6186971060167</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1794.4545140861105</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1773.6969160186632</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1738.0824261393575</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1621.7405382201393</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1749.0416570141369</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1760.2280493422027</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1644.8330858166323</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1629.0744318584823</v>
-      </c>
-      <c r="S8" s="3">
-        <v>1745.8377302460508</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1759.1160250476573</v>
-      </c>
-      <c r="U8" s="3">
-        <v>1776.9338861177446</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1669.6438385485037</v>
-      </c>
-      <c r="W8" s="3">
-        <v>1740.9672053339332</v>
-      </c>
-      <c r="X8" s="3">
-        <v>1604.4425332663868</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>1619.7611335164233</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>1614.4900393401706</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>1662.7117673098519</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1750.6844761715195</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>1647.9469870083865</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>1727.3986643169185</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>1749.5424656061498</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>1604.4425332663868</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>1704.9389509745777</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>1851.8347991012236</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>70.061468709685869</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>1739.5248157366455</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="B8" s="1">
+        <v>1761.6812670141353</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1736.6181836474091</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1622.0229832850346</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1643.718632367908</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1755.9877297874432</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1742.9329235177611</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1613.8753549086307</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1793.397425375578</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1650.3702877516243</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1872.8481891296053</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1652.6603213348631</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1882.2479245487332</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1640.8744257422304</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1639.4749595197022</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1865.2118348439526</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1615.0041040869778</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1643.3142540833671</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1744.3053007933493</v>
+      </c>
+      <c r="T8" s="1">
+        <v>1737.3669987139526</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1764.2444973506369</v>
+      </c>
+      <c r="V8" s="1">
+        <v>1719.9027513132146</v>
+      </c>
+      <c r="W8" s="1">
+        <v>1853.0844014577938</v>
+      </c>
+      <c r="X8" s="1">
+        <v>1727.0402469669782</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>1648.174925845821</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>1615.8326413674715</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>1907.2376811852605</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>1736.0133728507412</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>1743.5223806443803</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>1613.4266036725173</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>2031.4710464817003</v>
+      </c>
+      <c r="AF8">
+        <v>1613.4266036725173</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>1732.4621216529597</v>
+      </c>
+      <c r="AH8">
+        <v>2031.4710464817003</v>
+      </c>
+      <c r="AI8">
+        <v>105.35819570508359</v>
+      </c>
+      <c r="AJ8">
+        <v>1736.3157782490753</v>
+      </c>
+      <c r="AK8" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:37">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
-        <v>1609.178456910819</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1847.2792721245144</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1730.4796779238627</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1652.3926851093977</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1742.2903289546778</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1618.1925373697793</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1742.6003952371691</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1643.9407224690153</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1750.0318216523192</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1864.3682565935521</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1633.6123282434144</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1615.2906037143725</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1734.649679803744</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1608.92796468753</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1743.1691536472927</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1636.598629362117</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1657.2191319978999</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1664.7117053945412</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1641.5914266050663</v>
-      </c>
-      <c r="U9" s="3">
-        <v>1613.573095614996</v>
-      </c>
-      <c r="V9" s="3">
-        <v>1902.3442325057533</v>
-      </c>
-      <c r="W9" s="3">
-        <v>1753.839977186931</v>
-      </c>
-      <c r="X9" s="3">
-        <v>1742.2488097823414</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>1627.5080779007797</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1617.1926688478093</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>1639.0963385285679</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>1625.2108632698446</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>1839.8051552841109</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>1865.6012754754859</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>1723.0765932451529</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>1608.92796468753</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>1702.8673955147617</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>1902.3442325057533</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>89.309261133187206</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>1660.9654186962207</v>
-      </c>
-      <c r="AK9" s="3">
-        <v>3</v>
+      <c r="B9" s="1">
+        <v>1745.9936485811795</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1631.9110742987987</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1651.5879986587968</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1646.7495935246411</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1991.0623699240341</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1605.7783601491619</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1610.3432869969849</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1664.4025997114989</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1743.4707232366995</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1644.3898504416552</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1609.6904438059357</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1842.3758176954677</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1791.2389352165483</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1749.7877705990704</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1613.869229635495</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1656.3831638943882</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1747.6106408420555</v>
+      </c>
+      <c r="S9" s="1">
+        <v>1747.589606574445</v>
+      </c>
+      <c r="T9" s="1">
+        <v>1986.5358382477548</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1608.0019020531836</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1740.2321116606624</v>
+      </c>
+      <c r="W9" s="1">
+        <v>1649.4436183471089</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1756.3852885784067</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1657.4217637896586</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>1651.8794958874214</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>1622.5162175840492</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>1650.4737654775588</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>1663.9102438018278</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>1743.0657903975039</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>1624.5791374502628</v>
+      </c>
+      <c r="AF9">
+        <v>1605.7783601491619</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>1701.622676235409</v>
+      </c>
+      <c r="AH9">
+        <v>1991.0623699240341</v>
+      </c>
+      <c r="AI9">
+        <v>100.37308411289564</v>
+      </c>
+      <c r="AJ9">
+        <v>1656.9024638420233</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:37">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>1677.4205621754502</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2162.4781361123387</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2303.9648366026859</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2417.5855748205299</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1824.8854633037515</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2159.7933471156166</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1883.2242400843606</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2123.4077571795597</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2081.3474470425558</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2019.916790345954</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2397.2464688575756</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1986.6512593179718</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2161.1156045617631</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1970.2592152050333</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1831.5915671291714</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>2328.0169357397976</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2324.1643210112634</v>
-      </c>
-      <c r="S10" s="3">
-        <v>2058.4045422129238</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2085.3261538243023</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1965.7887558073278</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2196.0330233163313</v>
-      </c>
-      <c r="W10" s="3">
-        <v>2298.224092205488</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1892.5636523390135</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>2002.1804793032304</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>1632.045377981322</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>2058.2977086516976</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1752.8278656149587</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>2033.0941848382281</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1890.4479979067833</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>2140.0621266872913</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>1632.045377981322</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>2055.2788495764762</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>2417.5855748205299</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>204.00082760605443</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>2058.3511254323107</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>9</v>
+      <c r="B10" s="1">
+        <v>2048.8620433087794</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2303.2040297071499</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2076.8827778361233</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2058.6386821029337</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1934.0721266680339</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1703.7396382222316</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2125.9430758412796</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2065.6836839305756</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1896.9293901564452</v>
+      </c>
+      <c r="K10" s="1">
+        <v>2085.8012770753808</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2014.3314726104459</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1886.9495808406477</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2078.8912079286142</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2213.0939670914763</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1885.1632214205001</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2061.4994240411579</v>
+      </c>
+      <c r="R10" s="1">
+        <v>2179.5448506084658</v>
+      </c>
+      <c r="S10" s="1">
+        <v>2041.9733726732998</v>
+      </c>
+      <c r="T10" s="1">
+        <v>2171.6118768927658</v>
+      </c>
+      <c r="U10" s="1">
+        <v>1953.3138332430008</v>
+      </c>
+      <c r="V10" s="1">
+        <v>2041.8483018864063</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1920.8911851003431</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1968.4495640965979</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>2112.7399412410141</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>2004.443899418666</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>1917.9419972830178</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>2128.5466617699217</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>2028.5221544270612</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>1899.6760152975487</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>2160.6885976919048</v>
+      </c>
+      <c r="AF10">
+        <v>1703.7396382222316</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>2032.3292616803928</v>
+      </c>
+      <c r="AH10">
+        <v>2303.2040297071499</v>
+      </c>
+      <c r="AI10">
+        <v>121.98091009438534</v>
+      </c>
+      <c r="AJ10">
+        <v>2045.4177079910396</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:37">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1843.4051004861678</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2207.3116486232743</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2279.6089200822285</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2065.8468865008149</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2395.2411472843919</v>
-      </c>
-      <c r="G11" s="3">
-        <v>2271.4062950018993</v>
-      </c>
-      <c r="H11" s="3">
-        <v>2606.4972831571686</v>
-      </c>
-      <c r="I11" s="3">
-        <v>2024.0306503910483</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1879.777384303276</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1826.0839590117089</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2463.7614062073258</v>
-      </c>
-      <c r="M11" s="3">
-        <v>2482.0558132840806</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1998.1719353304002</v>
-      </c>
-      <c r="O11" s="3">
-        <v>2026.5888852904202</v>
-      </c>
-      <c r="P11" s="3">
-        <v>1639.6206904231271</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>2012.4240190902092</v>
-      </c>
-      <c r="R11" s="3">
-        <v>2308.9983345974179</v>
-      </c>
-      <c r="S11" s="3">
-        <v>2041.9993749044197</v>
-      </c>
-      <c r="T11" s="3">
-        <v>2315.9856643717567</v>
-      </c>
-      <c r="U11" s="3">
-        <v>2364.1780887780733</v>
-      </c>
-      <c r="V11" s="3">
-        <v>2281.0632014730932</v>
-      </c>
-      <c r="W11" s="3">
-        <v>2056.432110723109</v>
-      </c>
-      <c r="X11" s="3">
-        <v>1868.7782591247062</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>2011.9641243370152</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>2541.046875067866</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>1969.5155619328384</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>2105.1826821293098</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>2124.9840709738646</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>2184.2101592307536</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>2434.1287795229618</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>1639.6206904231271</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>2154.3433103878242</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>2606.4972831571686</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>236.97459951278069</v>
-      </c>
-      <c r="AJ11" s="3">
-        <v>2115.0833765515872</v>
-      </c>
-      <c r="AK11" s="3">
-        <v>10</v>
+      <c r="B11" s="1">
+        <v>2511.8097228187826</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2323.5099474344033</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2197.6845664508955</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2098.1836873376028</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2140.1930441636582</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2538.9400258896922</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1933.8486944273639</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1948.7392497622782</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2681.3473334464816</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2505.6046966108502</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2374.287956813881</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2278.1214186608986</v>
+      </c>
+      <c r="N11" s="1">
+        <v>2532.3018563196501</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2486.1602924732747</v>
+      </c>
+      <c r="P11" s="1">
+        <v>2519.3628018118984</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2396.36481420579</v>
+      </c>
+      <c r="R11" s="1">
+        <v>2153.3085213741851</v>
+      </c>
+      <c r="S11" s="1">
+        <v>1733.9585090890996</v>
+      </c>
+      <c r="T11" s="1">
+        <v>2079.8653263023484</v>
+      </c>
+      <c r="U11" s="1">
+        <v>2091.5780102456638</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1934.2438413300995</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1978.8745656420299</v>
+      </c>
+      <c r="X11" s="1">
+        <v>2418.5307429830782</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1772.7502217730093</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>2304.9046280708785</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>2436.2240689323153</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>2504.5770395046775</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>2253.682361899474</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>2442.713135948326</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>2251.7926910807191</v>
+      </c>
+      <c r="AF11">
+        <v>1733.9585090890996</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>2260.7821257601104</v>
+      </c>
+      <c r="AH11">
+        <v>2681.3473334464816</v>
+      </c>
+      <c r="AI11">
+        <v>247.63067113250983</v>
+      </c>
+      <c r="AJ11">
+        <v>2291.5130233658883</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:37">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>1917.6232780673186</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2382.4483407772245</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1960.2716748057451</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1838.8148791542501</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1904.2955248952103</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1962.6057664782168</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2069.467489709783</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1975.8033165622217</v>
-      </c>
-      <c r="J12" s="3">
-        <v>2190.0339641941955</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1877.2649146546642</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1871.372790770055</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2068.6627255117737</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2034.3379635361161</v>
-      </c>
-      <c r="O12" s="3">
-        <v>2007.6229922052555</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2298.2469908855314</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>2364.584619888562</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1978.3043619312257</v>
-      </c>
-      <c r="S12" s="3">
-        <v>2174.4136416525612</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1867.2204586285939</v>
-      </c>
-      <c r="U12" s="3">
-        <v>2218.5411455523645</v>
-      </c>
-      <c r="V12" s="3">
-        <v>2051.8403971060716</v>
-      </c>
-      <c r="W12" s="3">
-        <v>1847.4653712926981</v>
-      </c>
-      <c r="X12" s="3">
-        <v>1863.869870450023</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>2134.8282867067301</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>2139.9610413659016</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>2014.4004506824608</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1998.8441634618032</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>1922.6679040077524</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>1991.6734218502902</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>1928.8332625097351</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>1838.8148791542501</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>2028.5440336431443</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>2382.4483407772245</v>
-      </c>
-      <c r="AI12" s="3">
-        <v>150.57845888599826</v>
-      </c>
-      <c r="AJ12" s="3">
-        <v>1995.2587926560468</v>
-      </c>
-      <c r="AK12" s="3">
-        <v>7</v>
+      <c r="B12" s="1">
+        <v>1972.8401613778656</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2186.7928208912253</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1981.3318750668975</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2113.6459215682662</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2156.8542396557814</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1756.4537336999424</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2199.5543483403821</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2110.3391963035751</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2163.8268831903633</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2316.0722198245876</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2352.9343881770715</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1797.8267941235836</v>
+      </c>
+      <c r="N12" s="1">
+        <v>2061.4146488541701</v>
+      </c>
+      <c r="O12" s="1">
+        <v>2018.0970189213945</v>
+      </c>
+      <c r="P12" s="1">
+        <v>2079.8607358448835</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2142.2831791046292</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1844.3365647047408</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1978.9376259091964</v>
+      </c>
+      <c r="T12" s="1">
+        <v>2188.9996964538095</v>
+      </c>
+      <c r="U12" s="1">
+        <v>2105.2868898855277</v>
+      </c>
+      <c r="V12" s="1">
+        <v>2030.8560726815094</v>
+      </c>
+      <c r="W12" s="1">
+        <v>2359.6122098445467</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1882.7411852118207</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>2203.8950620937026</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>2149.2539163303381</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>2115.9500421573835</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>1747.0619974554538</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>2183.1383713175069</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>2087.0626570204959</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>2202.8335478894633</v>
+      </c>
+      <c r="AF12">
+        <v>1747.0619974554538</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>2083.0031334633372</v>
+      </c>
+      <c r="AH12">
+        <v>2359.6122098445467</v>
+      </c>
+      <c r="AI12">
+        <v>159.74741956029152</v>
+      </c>
+      <c r="AJ12">
+        <v>2111.9925589359209</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:37">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>2106.7458590811148</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1882.4722918401465</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2109.7661306656278</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2160.1189561472852</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2151.5983538732908</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2039.7227872109777</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1858.7872403183819</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1873.7650025493222</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1991.1204184907112</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1915.399004846061</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1988.5628494323582</v>
-      </c>
-      <c r="M13" s="3">
-        <v>2218.2691462621874</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1818.0873782661372</v>
-      </c>
-      <c r="O13" s="3">
-        <v>2295.4830264925199</v>
-      </c>
-      <c r="P13" s="3">
-        <v>1860.9901699434533</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>2049.0417268578426</v>
-      </c>
-      <c r="R13" s="3">
-        <v>2005.4187448658231</v>
-      </c>
-      <c r="S13" s="3">
-        <v>2232.7271621772252</v>
-      </c>
-      <c r="T13" s="3">
-        <v>2171.3209991570725</v>
-      </c>
-      <c r="U13" s="3">
-        <v>2132.2519878447729</v>
-      </c>
-      <c r="V13" s="3">
-        <v>2235.7680537412161</v>
-      </c>
-      <c r="W13" s="3">
-        <v>1937.6695787995197</v>
-      </c>
-      <c r="X13" s="3">
-        <v>1954.7878117021091</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>1846.6183974625403</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>2102.1507619156564</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>2127.0549579809672</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>2372.6245750338521</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>2287.0833307544208</v>
-      </c>
-      <c r="AD13" s="3">
-        <v>2114.8913984192377</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>1656.7665986071331</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>1656.7665986071331</v>
-      </c>
-      <c r="AG13" s="3">
-        <v>2049.9021566912984</v>
-      </c>
-      <c r="AH13" s="3">
-        <v>2372.6245750338521</v>
-      </c>
-      <c r="AI13" s="3">
-        <v>167.19703751579848</v>
-      </c>
-      <c r="AJ13" s="3">
-        <v>2075.5962443867493</v>
-      </c>
-      <c r="AK13" s="3">
-        <v>8</v>
+      <c r="B13" s="1">
+        <v>2095.1233090221076</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1969.71995416966</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2264.9201008090577</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2069.592460336381</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1936.8706804387969</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2336.6417560778718</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2456.5841978856633</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2282.3299763758673</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2228.2288827551097</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2320.8855325129671</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2004.3011830600269</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2077.6867583110784</v>
+      </c>
+      <c r="N13" s="1">
+        <v>2216.3758657250291</v>
+      </c>
+      <c r="O13" s="1">
+        <v>2191.07738260307</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1969.6507051998328</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>2170.8100813814617</v>
+      </c>
+      <c r="R13" s="1">
+        <v>2258.2687484482371</v>
+      </c>
+      <c r="S13" s="1">
+        <v>2068.4757790672297</v>
+      </c>
+      <c r="T13" s="1">
+        <v>2172.5291508276673</v>
+      </c>
+      <c r="U13" s="1">
+        <v>1993.4979398971132</v>
+      </c>
+      <c r="V13" s="1">
+        <v>2211.193037103842</v>
+      </c>
+      <c r="W13" s="1">
+        <v>2210.2782352601439</v>
+      </c>
+      <c r="X13" s="1">
+        <v>2144.0727136436581</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>2171.9068749329745</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>2425.8398201830591</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>1743.3268741528982</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>1829.2796422757319</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>1973.1842264495413</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>2107.8904145217512</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>1938.128837481438</v>
+      </c>
+      <c r="AF13">
+        <v>1743.3268741528982</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>2127.9557040303089</v>
+      </c>
+      <c r="AH13">
+        <v>2456.5841978856633</v>
+      </c>
+      <c r="AI13">
+        <v>166.78725421924779</v>
+      </c>
+      <c r="AJ13">
+        <v>2157.4413975125599</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
-        <v>2047.5031413157637</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1684.6126204801924</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2091.3431228505356</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2250.050395278522</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2013.3013816223147</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2038.6902765968284</v>
-      </c>
-      <c r="H14" s="3">
-        <v>2025.9335990300533</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2025.5771703497228</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2025.3649274192667</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1916.7109081726974</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1770.5523878452218</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1838.3065072436937</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2104.6333518791344</v>
-      </c>
-      <c r="O14" s="3">
-        <v>2037.8401558876039</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1966.2698953155591</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1787.6535828187352</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2061.5481160471281</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2167.8021780276817</v>
-      </c>
-      <c r="T14" s="3">
-        <v>2043.8896053164697</v>
-      </c>
-      <c r="U14" s="3">
-        <v>1943.3654933631312</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1869.8286501254322</v>
-      </c>
-      <c r="W14" s="3">
-        <v>1693.8006625110952</v>
-      </c>
-      <c r="X14" s="3">
-        <v>2017.0657716710866</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1884.5219454275862</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>1997.0066548716754</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>1872.6699189305837</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>1737.2467446012095</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>1650.5201710327492</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1992.7489443203103</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>1736.0661139609892</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>1650.5201710327492</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>1943.0808131437657</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>2250.050395278522</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>151.07671469310583</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>1994.8777995959929</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="B14" s="1">
+        <v>2036.9882616012392</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2024.3114162376248</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1814.5357544523026</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1992.3702657408508</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2141.55299732299</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2170.5396830436498</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2063.7404224896354</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2198.4541054943652</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2157.3346563770674</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1881.6401236600589</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2036.5232785316757</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2164.7427544768325</v>
+      </c>
+      <c r="N14" s="1">
+        <v>2113.244810527598</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2006.7815430052983</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1924.4214361647632</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>2086.832105107701</v>
+      </c>
+      <c r="R14" s="1">
+        <v>1993.4976002244262</v>
+      </c>
+      <c r="S14" s="1">
+        <v>2082.892681487222</v>
+      </c>
+      <c r="T14" s="1">
+        <v>2184.7559217988992</v>
+      </c>
+      <c r="U14" s="1">
+        <v>1972.4639862534173</v>
+      </c>
+      <c r="V14" s="1">
+        <v>1871.3755335934343</v>
+      </c>
+      <c r="W14" s="1">
+        <v>2014.4166516956939</v>
+      </c>
+      <c r="X14" s="1">
+        <v>1847.1265173231056</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>2027.2374391279393</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>2000.2868096712273</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>2017.860109643967</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>1992.768612926692</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2039.4586958274874</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>2053.5103392852557</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>2015.2532584132846</v>
+      </c>
+      <c r="AF14">
+        <v>1814.5357544523026</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>2030.8972590501903</v>
+      </c>
+      <c r="AH14">
+        <v>2198.4541054943652</v>
+      </c>
+      <c r="AI14">
+        <v>98.505706835465389</v>
+      </c>
+      <c r="AJ14">
+        <v>2025.7744276827821</v>
+      </c>
+      <c r="AK14" s="1">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9D0D55-6E98-4AF1-BC73-710FDCDF7026}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -13460,12 +13562,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4567F159-4C4E-44BC-90EB-82A9590F3A0B}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -15058,10 +15160,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16655,12 +16757,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9371C6-A5F3-4ADB-A64C-701C35E1870D}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -18253,10 +18355,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AY17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19865,19 +19967,11 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304E5416-9466-45F2-A415-B8CA2EECD02E}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" customWidth="1"/>
-    <col min="2" max="7" width="11.796875" customWidth="1"/>
-    <col min="8" max="8" width="11.86328125" customWidth="1"/>
-    <col min="9" max="17" width="11.796875" customWidth="1"/>
-    <col min="18" max="18" width="11.86328125" customWidth="1"/>
-    <col min="19" max="20" width="11.796875" customWidth="1"/>
-    <col min="21" max="21" width="11.86328125" customWidth="1"/>
-    <col min="22" max="28" width="11.796875" customWidth="1"/>
-    <col min="29" max="29" width="11.86328125" customWidth="1"/>
-    <col min="30" max="36" width="11.796875" customWidth="1"/>
-    <col min="37" max="37" width="5.19921875" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" customWidth="1"/>
+    <col min="2" max="36" width="11.81640625" customWidth="1"/>
+    <col min="37" max="37" width="5.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -21470,12 +21564,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107953A9-7D24-4DEF-B9E6-BCD32A22597F}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -23068,12 +23162,12 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A64C2C-AC90-4D4B-B62B-7EF0A9299853}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="9.06640625" style="3"/>
+    <col min="38" max="16384" width="9.08984375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -24667,10 +24761,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26264,10 +26358,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27861,12 +27955,12 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F47080E-A477-4037-BED1-3B05159AEAA1}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -29459,12 +29553,12 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A57091-397E-4B9B-BB4F-E8FD239D44C4}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -31057,10 +31151,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -32654,12 +32748,12 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85849CB4-07C9-4CE1-BE49-AAA6E9B0809C}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -34252,12 +34346,12 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB629C5-7502-4D25-BC48-9627EFEDF26F}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -35850,12 +35944,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="34" width="11.53125" customWidth="1"/>
-    <col min="35" max="35" width="15.19921875" customWidth="1"/>
-    <col min="36" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="34" width="11.54296875" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37449,10 +37543,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -39046,12 +39140,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D83DD98-3353-4D50-9EF1-589BC1DC8CB1}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -40644,12 +40738,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8939C7-0F22-400B-AAF2-87708EDD8411}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -42242,12 +42336,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA85E16-4F49-4507-A7B5-520DD8F3F44D}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="3" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="3" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" style="3" customWidth="1"/>
     <col min="37" max="37" width="5" style="3" customWidth="1"/>
-    <col min="38" max="16384" width="8.86328125" style="3"/>
+    <col min="38" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -43840,10 +43934,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -45437,10 +45531,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AK14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" customWidth="1"/>
-    <col min="2" max="36" width="11.53125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="2" max="36" width="11.54296875" customWidth="1"/>
     <col min="37" max="37" width="5" customWidth="1"/>
   </cols>
   <sheetData>
